--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>59.08177455615503</v>
+        <v>9.600788365375193</v>
       </c>
       <c r="D2" t="n">
-        <v>47.07558933365689</v>
+        <v>7.649783266719244</v>
       </c>
       <c r="E2" t="n">
-        <v>9.938997773252868</v>
+        <v>1.615087138153591</v>
       </c>
       <c r="F2" t="n">
-        <v>8.119553130215939</v>
+        <v>1.31942738366009</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.11083957911483</v>
+        <v>4.893011431606161</v>
       </c>
       <c r="D3" t="n">
-        <v>31.87486383413181</v>
+        <v>5.179665373046419</v>
       </c>
       <c r="E3" t="n">
-        <v>9.938997773252868</v>
+        <v>1.615087138153591</v>
       </c>
       <c r="F3" t="n">
-        <v>8.119553130215939</v>
+        <v>1.31942738366009</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.89661428052396</v>
+        <v>4.045699820585143</v>
       </c>
       <c r="D4" t="n">
-        <v>21.68265357932611</v>
+        <v>3.523431206640494</v>
       </c>
       <c r="E4" t="n">
-        <v>9.938997773252868</v>
+        <v>1.615087138153591</v>
       </c>
       <c r="F4" t="n">
-        <v>8.119553130215939</v>
+        <v>1.31942738366009</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.84460353520437</v>
+        <v>6.47474807447071</v>
       </c>
       <c r="D5" t="n">
-        <v>38.96430105525688</v>
+        <v>6.331698921479243</v>
       </c>
       <c r="E5" t="n">
-        <v>9.938997773252868</v>
+        <v>1.615087138153591</v>
       </c>
       <c r="F5" t="n">
-        <v>8.119553130215939</v>
+        <v>1.31942738366009</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.86494734748746</v>
+        <v>5.178053943966712</v>
       </c>
       <c r="D6" t="n">
-        <v>30.91113479175338</v>
+        <v>5.023059403659924</v>
       </c>
       <c r="E6" t="n">
-        <v>9.938997773252868</v>
+        <v>1.615087138153591</v>
       </c>
       <c r="F6" t="n">
-        <v>8.119553130215939</v>
+        <v>1.31942738366009</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>50.53624956254066</v>
+        <v>8.212140553912858</v>
       </c>
       <c r="D7" t="n">
-        <v>49.62108891383645</v>
+        <v>8.063426948498423</v>
       </c>
       <c r="E7" t="n">
-        <v>9.938997773252868</v>
+        <v>1.615087138153591</v>
       </c>
       <c r="F7" t="n">
-        <v>8.119553130215939</v>
+        <v>1.31942738366009</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.3559888963233</v>
+        <v>6.720348195652535</v>
       </c>
       <c r="D8" t="n">
-        <v>40.36771020336981</v>
+        <v>6.559752908047594</v>
       </c>
       <c r="E8" t="n">
-        <v>9.938997773252868</v>
+        <v>1.615087138153591</v>
       </c>
       <c r="F8" t="n">
-        <v>8.119553130215939</v>
+        <v>1.31942738366009</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>50.01513047965094</v>
+        <v>8.127458702943278</v>
       </c>
       <c r="D9" t="n">
-        <v>46.79411995785109</v>
+        <v>7.604044493150802</v>
       </c>
       <c r="E9" t="n">
-        <v>9.938997773252868</v>
+        <v>1.615087138153591</v>
       </c>
       <c r="F9" t="n">
-        <v>8.119553130215939</v>
+        <v>1.31942738366009</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.24805618577906</v>
+        <v>6.377809130189097</v>
       </c>
       <c r="D10" t="n">
-        <v>36.86641747837938</v>
+        <v>5.99079284023665</v>
       </c>
       <c r="E10" t="n">
-        <v>9.938997773252868</v>
+        <v>1.615087138153591</v>
       </c>
       <c r="F10" t="n">
-        <v>8.119553130215939</v>
+        <v>1.31942738366009</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>45.85704278226033</v>
+        <v>7.451769452117304</v>
       </c>
       <c r="D11" t="n">
-        <v>40.12249376205114</v>
+        <v>6.51990523633331</v>
       </c>
       <c r="E11" t="n">
-        <v>9.938997773252868</v>
+        <v>1.615087138153591</v>
       </c>
       <c r="F11" t="n">
-        <v>8.119553130215939</v>
+        <v>1.31942738366009</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
